--- a/data/trans_orig/P36BPD01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023</t>
+          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>473894</t>
+          <t>473790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>493123</t>
+          <t>493890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>702773</t>
+          <t>700995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>721851</t>
+          <t>720657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1182993</t>
+          <t>1183218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1211082</t>
+          <t>1210444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>40152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49987</t>
+          <t>51765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55619</t>
+          <t>56257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83708</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2121791</t>
+          <t>2120357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2192946</t>
+          <t>2191060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2106644</t>
+          <t>2108170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2161380</t>
+          <t>2162329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4246217</t>
+          <t>4242915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4334265</t>
+          <t>4335131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82112</t>
+          <t>83998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153267</t>
+          <t>154701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72836</t>
+          <t>71887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127572</t>
+          <t>126046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175008</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263056</t>
+          <t>266358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>617920</t>
+          <t>617868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>636098</t>
+          <t>636137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>629415</t>
+          <t>630228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>646669</t>
+          <t>647290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1253731</t>
+          <t>1253434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1278581</t>
+          <t>1278998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26662</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3232646</t>
+          <t>3231490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3308830</t>
+          <t>3306442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3457344</t>
+          <t>3457088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3516697</t>
+          <t>3514302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6711749</t>
+          <t>6709085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6806098</t>
+          <t>6807245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124949</t>
+          <t>127337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201133</t>
+          <t>202289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130741</t>
+          <t>133136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190094</t>
+          <t>190350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275119</t>
+          <t>273972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369468</t>
+          <t>372132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>484941</t>
+          <t>536102</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>473790</t>
+          <t>522791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>493890</t>
+          <t>547454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>712261</t>
+          <t>771574</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>700995</t>
+          <t>760558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>720657</t>
+          <t>782733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1197202</t>
+          <t>1307675</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1183218</t>
+          <t>1289992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1210444</t>
+          <t>1323586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29001</t>
+          <t>41440</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40152</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40499</t>
+          <t>47562</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>36403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>58578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>69499</t>
+          <t>89003</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56257</t>
+          <t>73092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83483</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752760</t>
+          <t>819136</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752760</t>
+          <t>819136</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752760</t>
+          <t>819136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266701</t>
+          <t>1396678</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266701</t>
+          <t>1396678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266701</t>
+          <t>1396678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2155002</t>
+          <t>2062702</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2120357</t>
+          <t>2028900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2191060</t>
+          <t>2091625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2133488</t>
+          <t>2038900</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2108170</t>
+          <t>2014703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2162329</t>
+          <t>2058984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4288489</t>
+          <t>4101602</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4242915</t>
+          <t>4063124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4335131</t>
+          <t>4136408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>120056</t>
+          <t>153473</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83998</t>
+          <t>124550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154701</t>
+          <t>187275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100728</t>
+          <t>127886</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71887</t>
+          <t>107802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126046</t>
+          <t>152083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>281359</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174142</t>
+          <t>246553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266358</t>
+          <t>319837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2275058</t>
+          <t>2216175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2275058</t>
+          <t>2216175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2275058</t>
+          <t>2216175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234216</t>
+          <t>2166786</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234216</t>
+          <t>2166786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234216</t>
+          <t>2166786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4509273</t>
+          <t>4382961</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4509273</t>
+          <t>4382961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4509273</t>
+          <t>4382961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>628738</t>
+          <t>688924</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>617868</t>
+          <t>675052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>636137</t>
+          <t>696972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>640023</t>
+          <t>707155</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>630228</t>
+          <t>693652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>647290</t>
+          <t>715442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1268761</t>
+          <t>1396079</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1253434</t>
+          <t>1380286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1278998</t>
+          <t>1409534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>34640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>41225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26245</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644780</t>
+          <t>709692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644780</t>
+          <t>709692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644780</t>
+          <t>709692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305243</t>
+          <t>1444569</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305243</t>
+          <t>1444569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305243</t>
+          <t>1444569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3268680</t>
+          <t>3287728</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3231490</t>
+          <t>3248944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3306442</t>
+          <t>3319811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3485771</t>
+          <t>3517629</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3457088</t>
+          <t>3488477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3514302</t>
+          <t>3541177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6754451</t>
+          <t>6805356</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6709085</t>
+          <t>6761817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6807245</t>
+          <t>6847974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>165099</t>
+          <t>215681</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127337</t>
+          <t>183598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202289</t>
+          <t>254465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161667</t>
+          <t>203171</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133136</t>
+          <t>179623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190350</t>
+          <t>232323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326766</t>
+          <t>418852</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273972</t>
+          <t>376234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372132</t>
+          <t>462391</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3433779</t>
+          <t>3503409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3433779</t>
+          <t>3503409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3433779</t>
+          <t>3503409</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647438</t>
+          <t>3720800</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647438</t>
+          <t>3720800</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647438</t>
+          <t>3720800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7081217</t>
+          <t>7224208</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7081217</t>
+          <t>7224208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7081217</t>
+          <t>7224208</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
